--- a/request_forms/034_treadmill_repair_form_template--request_forms.xlsx
+++ b/request_forms/034_treadmill_repair_form_template--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Time Zone Hint</t>
+          <t>Main Page 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Main Page 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Main Page 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Main Page 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>main_page_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>main_page_7_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>main_page_7_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>main_page_9_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>main_page_9_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>main_page_18_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>main_page_choices</t>
+          <t>main_page_18_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
